--- a/registration_forms/001_panel_application_form--registration_forms.xlsx
+++ b/registration_forms/001_panel_application_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10000,_'name':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10000, 'name': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_10001,_'name':_'institution'}</t>
+          <t>institution</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 10001, 'name': 'Institution'}</t>
+          <t>Institution</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_10002,_'name':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 10002, 'name': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10003,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10003, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_10004,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 10004, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10005,_'name':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10005, 'name': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_10006,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 10006, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_10007,_'name':_'another_tool'}</t>
+          <t>another_tool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 10007, 'name': 'another_tool'}</t>
+          <t>another tool</t>
         </is>
       </c>
     </row>
